--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/dic-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6863.16</v>
+        <v>6774.45</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>925.59</v>
+        <v>913.63</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7178.2</v>
+        <v>7085.42</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>785.1799999999999</v>
+        <v>775.03</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2253.18</v>
+        <v>2224.06</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3270.72</v>
+        <v>3228.44</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1045.35</v>
+        <v>1031.84</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>759.15</v>
+        <v>749.34</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>773.48</v>
+        <v>763.48</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2036.67</v>
+        <v>2010.34</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1323.47</v>
+        <v>1306.36</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1682.95</v>
+        <v>1661.2</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>988.04</v>
+        <v>975.27</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3006.35</v>
+        <v>2967.49</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>973.37</v>
+        <v>960.79</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2313.52</v>
+        <v>2283.62</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13486.33</v>
+        <v>13312.01</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1453.99</v>
+        <v>1435.2</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>925.59</v>
+        <v>913.63</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5577.99</v>
+        <v>5505.89</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5587.95</v>
+        <v>5515.72</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1166.08</v>
+        <v>1151.27</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1421.6</v>
+        <v>1403.54</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1394.04</v>
+        <v>1376.33</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1263.07</v>
+        <v>1247.02</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2417.76</v>
+        <v>2387.05</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>923.1900000000001</v>
+        <v>911.46</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>869.35</v>
+        <v>858.3099999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1183.64</v>
+        <v>1168.6</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1481.14</v>
+        <v>1462.33</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5297.35</v>
+        <v>5230.06</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3154.24</v>
+        <v>3114.18</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1788.42</v>
+        <v>1765.71</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>970.92</v>
+        <v>958.59</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>815.71</v>
+        <v>805.35</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1255.47</v>
+        <v>1239.53</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2123.47</v>
+        <v>2096.5</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1020.26</v>
+        <v>1007.3</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2987.47</v>
+        <v>2949.53</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1224.88</v>
+        <v>1209.32</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1084.82</v>
+        <v>1071.04</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2470.19</v>
+        <v>2438.81</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4222.94</v>
+        <v>4169.3</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2444.18</v>
+        <v>2413.13</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1656.35</v>
+        <v>1635.31</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1457.75</v>
+        <v>1439.23</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1154.35</v>
+        <v>1139.69</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1483.77</v>
+        <v>1464.93</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>9294.879999999999</v>
+        <v>9176.809999999999</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11810.86</v>
+        <v>11660.83</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8126.35</v>
+        <v>8023.13</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1233.73</v>
+        <v>1218.06</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7889.2</v>
+        <v>7788.99</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5116.76</v>
+        <v>5051.76</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1501.94</v>
+        <v>1482.86</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4684.4</v>
+        <v>4624.9</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1253.77</v>
+        <v>1237.85</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>943.78</v>
+        <v>931.79</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>11879.44</v>
+        <v>11728.54</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4059.72</v>
+        <v>4008.16</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2307.8</v>
+        <v>2278.49</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3455.06</v>
+        <v>3411.18</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>9519.48</v>
+        <v>9398.559999999999</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>879.61</v>
+        <v>868.4400000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2822.18</v>
+        <v>2786.33</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1634.22</v>
+        <v>1613.46</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5457.53</v>
+        <v>5388.21</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2732.2</v>
+        <v>2697.49</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2149.93</v>
+        <v>2122.62</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2001.34</v>
+        <v>1981.43</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1365.71</v>
+        <v>1352.12</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1257.03</v>
+        <v>1244.53</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1515.2</v>
+        <v>1500.13</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>778.38</v>
+        <v>770.63</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1376.28</v>
+        <v>1362.59</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1975.94</v>
+        <v>1956.29</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1906.84</v>
+        <v>1887.87</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3120.73</v>
+        <v>3089.68</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2143.18</v>
+        <v>2121.85</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2284.73</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>12941.19</v>
+        <v>12812.43</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>6263.64</v>
+        <v>6201.32</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>761.75</v>
+        <v>754.17</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>847.4</v>
+        <v>838.97</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1746.7</v>
+        <v>1729.32</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3385.55</v>
+        <v>3351.86</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>760.62</v>
+        <v>753.05</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1051.98</v>
+        <v>1041.51</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>5104.22</v>
+        <v>5053.44</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2728.54</v>
+        <v>2701.4</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2570.9</v>
+        <v>2545.32</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>20854.38</v>
+        <v>20646.89</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1075.78</v>
+        <v>1065.08</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2864.32</v>
+        <v>2835.83</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1934.84</v>
+        <v>1915.59</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1898.62</v>
+        <v>1879.73</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2552.58</v>
+        <v>2527.19</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>783.35</v>
+        <v>775.5599999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>959.36</v>
+        <v>949.8200000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>759.4299999999999</v>
+        <v>751.88</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2184.58</v>
+        <v>2176.75</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>36374.94</v>
+        <v>36244.51</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>8720.719999999999</v>
+        <v>8689.450000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2703.68</v>
+        <v>2693.99</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1716.63</v>
+        <v>1710.48</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>794.3099999999999</v>
+        <v>791.47</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>4218.68</v>
+        <v>4203.56</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>5164.28</v>
+        <v>5145.76</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1840.17</v>
+        <v>1833.57</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>875.9</v>
+        <v>872.76</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1555.43</v>
+        <v>1549.85</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>43697.42</v>
+        <v>43540.73</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>8484.389999999999</v>
+        <v>8453.959999999999</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2111.94</v>
+        <v>2104.37</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2632.43</v>
+        <v>2622.99</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>760.55</v>
+        <v>757.83</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>8589.93</v>
+        <v>8559.129999999999</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>6994.29</v>
+        <v>6969.21</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5366.4</v>
+        <v>5347.16</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>7123.38</v>
+        <v>7097.84</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1264.99</v>
+        <v>1260.46</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>27923.66</v>
+        <v>27823.53</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2217.21</v>
+        <v>2209.26</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1123.51</v>
+        <v>1119.48</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3165.45</v>
+        <v>3154.1</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1795.4</v>
+        <v>1788.96</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>924.29</v>
+        <v>920.98</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1522.45</v>
+        <v>1519.15</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>959.47</v>
+        <v>957.4</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>4967.25</v>
+        <v>4956.5</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2326.32</v>
+        <v>2321.29</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>21876.63</v>
+        <v>21829.28</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1877.94</v>
+        <v>1873.88</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1249.56</v>
+        <v>1246.85</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1339.45</v>
+        <v>1336.55</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>834.63</v>
+        <v>832.83</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1526.96</v>
+        <v>1523.65</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>766.48</v>
+        <v>764.8200000000001</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>7119.23</v>
+        <v>7103.82</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1111.98</v>
+        <v>1109.58</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1014.08</v>
+        <v>1011.89</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>7483.31</v>
+        <v>7467.11</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>847.26</v>
+        <v>845.4299999999999</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>834.46</v>
+        <v>832.66</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>10185.95</v>
+        <v>10163.91</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>760.5599999999999</v>
+        <v>758.91</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>803.3200000000001</v>
+        <v>801.58</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>9813.93</v>
+        <v>9792.700000000001</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>4979.58</v>
+        <v>4968.8</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2873.93</v>
+        <v>2867.71</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1790.31</v>
+        <v>1786.44</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2395.16</v>
+        <v>2389.98</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>915.72</v>
+        <v>913.74</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1607.26</v>
+        <v>1603.78</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>5441.4</v>
+        <v>5429.62</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>828.7</v>
+        <v>826.9</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>17899.04</v>
+        <v>17860.3</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2554.28</v>
+        <v>2548.75</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3519.81</v>
+        <v>3512.19</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>15241.67</v>
+        <v>15208.68</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1273.93</v>
+        <v>1271.18</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1291.11</v>
+        <v>1288.31</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2188.24</v>
+        <v>2183.5</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>6748.89</v>
+        <v>6734.28</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2535.52</v>
+        <v>2530.03</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1158.54</v>
+        <v>1156.04</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2215.66</v>
+        <v>2210.87</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>791.75</v>
+        <v>790.04</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>790.95</v>
+        <v>787.63</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2005.11</v>
+        <v>1996.7</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>771.5700000000001</v>
+        <v>768.34</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4190.5</v>
+        <v>4172.93</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>8470.75</v>
+        <v>8435.24</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1456.83</v>
+        <v>1450.72</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>759.47</v>
+        <v>756.28</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1193.97</v>
+        <v>1188.97</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1397.43</v>
+        <v>1391.57</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3168.79</v>
+        <v>3155.5</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2193.19</v>
+        <v>2183.99</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2663.42</v>
+        <v>2652.26</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1199.07</v>
+        <v>1194.04</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>785.01</v>
+        <v>781.72</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3838.24</v>
+        <v>3822.15</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>800.59</v>
+        <v>797.24</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2139.8</v>
+        <v>2130.83</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2727.34</v>
+        <v>2715.91</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1023.18</v>
+        <v>1018.89</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1695.84</v>
+        <v>1688.73</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>28234.03</v>
+        <v>28115.67</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>783.4</v>
+        <v>780.12</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1359.94</v>
+        <v>1354.24</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1077.73</v>
+        <v>1073.21</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3905.26</v>
+        <v>3888.89</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2865.1</v>
+        <v>2853.09</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>10627.56</v>
+        <v>10583.01</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>32930.89</v>
+        <v>32792.84</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>9319.290000000001</v>
+        <v>9280.219999999999</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1790.53</v>
+        <v>1783.02</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>4684.08</v>
+        <v>4664.44</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>4821.68</v>
+        <v>4801.47</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>5385.45</v>
+        <v>5362.88</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5191.04</v>
+        <v>5169.27</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>764.02</v>
+        <v>760.8200000000001</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2976.94</v>
+        <v>2964.46</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>778.66</v>
+        <v>775.39</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>10884.04</v>
+        <v>10838.41</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1243.56</v>
+        <v>1238.35</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3048.69</v>
+        <v>3035.91</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1789.83</v>
+        <v>1782.32</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>801.55</v>
+        <v>792.27</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>767.41</v>
+        <v>758.53</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>11547.71</v>
+        <v>11414.07</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>945.91</v>
+        <v>934.96</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>3909.57</v>
+        <v>3864.33</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1552.95</v>
+        <v>1534.98</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>868.51</v>
+        <v>858.46</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>925.51</v>
+        <v>914.8</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>795.17</v>
+        <v>785.97</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2465.54</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>20502.94</v>
+        <v>20265.65</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1011.19</v>
+        <v>999.49</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>3773.46</v>
+        <v>3729.79</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>917.2</v>
+        <v>906.59</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1248.88</v>
+        <v>1234.43</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>6868.47</v>
+        <v>6788.98</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1527.8</v>
+        <v>1510.12</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2111.68</v>
+        <v>2087.24</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>781.9400000000001</v>
+        <v>772.89</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1002.61</v>
+        <v>991</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1972.07</v>
+        <v>1949.25</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1084.38</v>
+        <v>1071.83</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>17652.61</v>
+        <v>17448.32</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1890.13</v>
+        <v>1868.25</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4564.71</v>
+        <v>4511.88</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2035.24</v>
+        <v>2011.69</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2908.48</v>
+        <v>2874.82</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>9458.91</v>
+        <v>9349.450000000001</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>8804.639999999999</v>
+        <v>8702.74</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1184.27</v>
+        <v>1170.56</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>769.99</v>
+        <v>761.0700000000001</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>14045.63</v>
+        <v>13883.08</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>4537.51</v>
+        <v>4484.99</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1359.16</v>
+        <v>1343.43</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1211.43</v>
+        <v>1197.41</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1572.38</v>
+        <v>1554.18</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>2094.46</v>
+        <v>2070.22</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>779.72</v>
+        <v>773.11</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1671.94</v>
+        <v>1657.78</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>3890.45</v>
+        <v>3857.5</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2855.74</v>
+        <v>2831.55</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>802.46</v>
+        <v>795.66</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>11046.64</v>
+        <v>10953.07</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2564.02</v>
+        <v>2542.3</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>34103.54</v>
+        <v>33814.65</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1526.37</v>
+        <v>1513.44</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2561.23</v>
+        <v>2539.53</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>3643.23</v>
+        <v>3612.37</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2145.6</v>
+        <v>2127.43</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>2480.03</v>
+        <v>2459.03</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>37545.14</v>
+        <v>37227.1</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>2356.44</v>
+        <v>2336.48</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>3179.57</v>
+        <v>3152.64</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>10241.57</v>
+        <v>10154.82</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1819.88</v>
+        <v>1804.47</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>4596.92</v>
+        <v>4557.98</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>13094.42</v>
+        <v>12983.5</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2010.65</v>
+        <v>1993.62</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>877.59</v>
+        <v>870.15</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>8719.950000000001</v>
+        <v>8646.09</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3652.52</v>
+        <v>3621.58</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3034.79</v>
+        <v>3009.08</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>934.23</v>
+        <v>926.3200000000001</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1744.73</v>
+        <v>1729.95</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1033.12</v>
+        <v>1024.37</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1270.28</v>
+        <v>1259.52</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>3192.34</v>
+        <v>3165.3</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>8323.32</v>
+        <v>8252.82</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>764.3099999999999</v>
+        <v>757.83</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1983.11</v>
+        <v>1966.31</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>789.66</v>
+        <v>782.97</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>3007.73</v>
+        <v>2982.25</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>760.5</v>
+        <v>754.05</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>765.54</v>
+        <v>764.9299999999999</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>787.58</v>
+        <v>786.9400000000001</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1366.91</v>
+        <v>1365.81</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>3817.62</v>
+        <v>3814.55</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>7642.96</v>
+        <v>7636.82</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>3221.3</v>
+        <v>3218.71</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>74999.23</v>
+        <v>74938.94</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1061.05</v>
+        <v>1060.2</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1072.12</v>
+        <v>1071.26</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>7178.89</v>
+        <v>7173.12</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3469.23</v>
+        <v>3466.44</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2182.79</v>
+        <v>2181.04</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>4302.44</v>
+        <v>4298.98</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>5102.43</v>
+        <v>5098.33</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>1161.83</v>
+        <v>1160.89</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>10497.09</v>
+        <v>10488.65</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>13761.28</v>
+        <v>13750.22</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2254.05</v>
+        <v>2252.23</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1934.19</v>
+        <v>1932.63</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>25140.08</v>
+        <v>25119.88</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>837.5</v>
+        <v>836.8200000000001</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>994.4299999999999</v>
+        <v>993.64</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>30381.07</v>
+        <v>30356.65</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2598.83</v>
+        <v>2596.74</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>808.02</v>
+        <v>807.37</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>823.99</v>
+        <v>823.33</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>919.5599999999999</v>
+        <v>918.8200000000001</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>7571.49</v>
+        <v>7565.41</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>9409.27</v>
+        <v>9401.700000000001</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>68851.05</v>
+        <v>68795.71000000001</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>763.59</v>
+        <v>762.98</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>3398.85</v>
+        <v>3396.12</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1081.05</v>
+        <v>1080.18</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>3189.72</v>
+        <v>3187.16</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>5001.37</v>
+        <v>4997.35</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1155.76</v>
+        <v>1154.83</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>3521.31</v>
+        <v>3518.48</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>784.21</v>
+        <v>783.58</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1524.84</v>
+        <v>1523.61</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>762.61</v>
+        <v>762</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1262.59</v>
+        <v>1267.43</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>3144.52</v>
+        <v>3156.59</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>19964.19</v>
+        <v>20040.81</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1495.71</v>
+        <v>1501.45</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2968.77</v>
+        <v>2980.16</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>779.46</v>
+        <v>782.45</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1537.75</v>
+        <v>1543.65</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1709.66</v>
+        <v>1716.22</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>839.9400000000001</v>
+        <v>843.16</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>16022.75</v>
+        <v>16084.25</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>6340.95</v>
+        <v>6365.29</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3273.14</v>
+        <v>3285.71</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>3131.06</v>
+        <v>3143.08</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1026.26</v>
+        <v>1030.2</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>13596.81</v>
+        <v>13649</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>2267.69</v>
+        <v>2276.4</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>881.95</v>
+        <v>885.34</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>10503.99</v>
+        <v>10544.3</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>759.38</v>
+        <v>762.29</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>4881.74</v>
+        <v>4900.47</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2129.28</v>
+        <v>2137.45</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1923.92</v>
+        <v>1931.31</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>7703.75</v>
+        <v>7733.32</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>984.33</v>
+        <v>988.1</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>2012.28</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>2758.98</v>
+        <v>2769.57</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2216.18</v>
+        <v>2224.68</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>2379.24</v>
+        <v>2388.37</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1226.37</v>
+        <v>1231.08</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>5143.94</v>
+        <v>5163.69</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>4074.25</v>
+        <v>4089.88</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>27745.32</v>
+        <v>27851.81</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>1102.67</v>
+        <v>1106.9</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>767.52</v>
+        <v>770.46</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>780.83</v>
+        <v>784.37</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>10186.91</v>
+        <v>10233.08</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1539.19</v>
+        <v>1546.17</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>970.3200000000001</v>
+        <v>974.72</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>3949.53</v>
+        <v>3967.42</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>3640.64</v>
+        <v>3657.14</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>13626.71</v>
+        <v>13688.46</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1321.02</v>
+        <v>1327.01</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2111.99</v>
+        <v>2121.56</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1211.09</v>
+        <v>1216.58</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>4908.68</v>
+        <v>4930.93</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1721.56</v>
+        <v>1729.36</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>4241.02</v>
+        <v>4260.24</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>12970.82</v>
+        <v>13029.6</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>19547.66</v>
+        <v>19636.24</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>3982.35</v>
+        <v>4000.4</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>765.62</v>
+        <v>769.09</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>5792.76</v>
+        <v>5819.01</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>1119.16</v>
+        <v>1124.23</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1309.64</v>
+        <v>1315.58</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1619.23</v>
+        <v>1626.57</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>2270.99</v>
+        <v>2281.28</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>986.97</v>
+        <v>991.4400000000001</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>4097.3</v>
+        <v>4115.87</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>853.61</v>
+        <v>857.48</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>2329.95</v>
+        <v>2340.5</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>775.05</v>
+        <v>778.5599999999999</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>759.85</v>
+        <v>763.3</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>946.76</v>
+        <v>951.0599999999999</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>815.97</v>
+        <v>819.66</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>8305.09</v>
+        <v>8342.73</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>3423.12</v>
+        <v>3438.63</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>24948.5</v>
+        <v>25061.55</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>21016.02</v>
+        <v>21111.26</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>5797.49</v>
+        <v>5823.76</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>68337.89</v>
+        <v>68647.57000000001</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>4251.93</v>
+        <v>4271.2</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>11997.67</v>
+        <v>12052.04</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>1975.62</v>
+        <v>1984.57</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1505.6</v>
+        <v>1512.43</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>760.7</v>
+        <v>764.15</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1863.92</v>
+        <v>1872.36</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1283.96</v>
+        <v>1289.78</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>3099.94</v>
+        <v>3113.99</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>33317.17</v>
+        <v>33468.16</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>7641.11</v>
+        <v>7675.74</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>7724.84</v>
+        <v>7759.85</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>2047.89</v>
+        <v>2053.32</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>1890.49</v>
+        <v>1895.5</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2196.54</v>
+        <v>2202.36</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>3372.78</v>
+        <v>3381.73</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1274.31</v>
+        <v>1277.69</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>771.67</v>
+        <v>773.71</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>804.23</v>
+        <v>806.37</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1985.73</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>872.37</v>
+        <v>874.6799999999999</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>779.0700000000001</v>
+        <v>781.13</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>2450.16</v>
+        <v>2456.66</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>776.98</v>
+        <v>779.04</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>2182.82</v>
+        <v>2188.6</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>2956.94</v>
+        <v>2964.78</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1364.75</v>
+        <v>1368.37</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>4647.58</v>
+        <v>4659.9</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>763.63</v>
+        <v>765.65</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>1663.77</v>
+        <v>1668.18</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>1058.24</v>
+        <v>1061.04</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>941.01</v>
+        <v>943.51</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>1472.82</v>
+        <v>1476.72</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>6831.05</v>
+        <v>6849.16</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>4408.84</v>
+        <v>4420.53</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>14710.24</v>
+        <v>14749.24</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>763.35</v>
+        <v>765.37</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>1138.26</v>
+        <v>1141.28</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>4177.85</v>
+        <v>4188.92</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2127.74</v>
+        <v>2133.38</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>1378.91</v>
+        <v>1382.56</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>7451.12</v>
+        <v>7470.88</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>2332.92</v>
+        <v>2339.11</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>21831.95</v>
+        <v>21889.85</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>789.74</v>
+        <v>791.84</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>1934.57</v>
+        <v>1939.7</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2411.86</v>
+        <v>2418.26</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>8505.139999999999</v>
+        <v>8527.690000000001</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>833.42</v>
+        <v>835.63</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>1674.82</v>
+        <v>1679.26</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>11175.96</v>
+        <v>11205.59</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1830.14</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>931.96</v>
+        <v>934.4299999999999</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>2004.16</v>
+        <v>2009.47</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2037.34</v>
+        <v>2042.74</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>1469.86</v>
+        <v>1473.76</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>2299.24</v>
+        <v>2305.34</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>880.27</v>
+        <v>882.6</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>1925.1</v>
+        <v>1930.2</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>3862.67</v>
+        <v>3872.91</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>9007.84</v>
+        <v>9031.73</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>5558.83</v>
+        <v>5573.57</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>5250.66</v>
+        <v>5264.58</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>11132.66</v>
+        <v>11162.18</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>1806.53</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>75640.87</v>
+        <v>75534.75999999999</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>1503.23</v>
+        <v>1501.12</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>763.53</v>
+        <v>762.46</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>766.47</v>
+        <v>765.39</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>762.64</v>
+        <v>761.5700000000001</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>953.62</v>
+        <v>952.29</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>3285.26</v>
+        <v>3280.65</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>3194.26</v>
+        <v>3189.78</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>2832.89</v>
+        <v>2828.92</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>3491.91</v>
+        <v>3487.01</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>9494.93</v>
+        <v>9481.610000000001</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>2112.84</v>
+        <v>2109.88</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2663.77</v>
+        <v>2660.04</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>1336.71</v>
+        <v>1334.83</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>1091.11</v>
+        <v>1089.58</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>11898.27</v>
+        <v>11881.58</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>2421.28</v>
+        <v>2417.88</v>
       </c>
     </row>
     <row r="475">
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>789.85</v>
+        <v>788.74</v>
       </c>
     </row>
     <row r="476">
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>772.97</v>
+        <v>771.89</v>
       </c>
     </row>
     <row r="477">
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>47420.08</v>
+        <v>47353.56</v>
       </c>
     </row>
     <row r="478">
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>760.21</v>
+        <v>759.14</v>
       </c>
     </row>
     <row r="479">
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>1911.58</v>
+        <v>1908.9</v>
       </c>
     </row>
     <row r="480">
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>764.8200000000001</v>
+        <v>763.75</v>
       </c>
     </row>
     <row r="481">
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>5202.43</v>
+        <v>5195.13</v>
       </c>
     </row>
     <row r="482">
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>3796.24</v>
+        <v>3790.92</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>817.74</v>
+        <v>816.59</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>7055.6</v>
+        <v>7045.7</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>2024.39</v>
+        <v>2021.55</v>
       </c>
     </row>
     <row r="486">
@@ -30093,7 +30093,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>3526.14</v>
+        <v>3521.19</v>
       </c>
     </row>
     <row r="487">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>3354.11</v>
+        <v>3349.41</v>
       </c>
     </row>
     <row r="488">
@@ -30215,7 +30215,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>4375.78</v>
+        <v>4369.64</v>
       </c>
     </row>
     <row r="489">
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>2182.48</v>
+        <v>2179.41</v>
       </c>
     </row>
     <row r="490">
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>23683.3</v>
+        <v>23650.08</v>
       </c>
     </row>
     <row r="491">
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>760.1900000000001</v>
+        <v>759.12</v>
       </c>
     </row>
     <row r="492">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>768.1</v>
+        <v>767.02</v>
       </c>
     </row>
     <row r="493">
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>763.3200000000001</v>
+        <v>762.25</v>
       </c>
     </row>
     <row r="494">
@@ -30581,7 +30581,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>775.52</v>
+        <v>774.4299999999999</v>
       </c>
     </row>
     <row r="495">
@@ -30642,7 +30642,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>4256.74</v>
+        <v>4250.77</v>
       </c>
     </row>
     <row r="496">
@@ -30703,7 +30703,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>762.14</v>
+        <v>761.0700000000001</v>
       </c>
     </row>
     <row r="497">
@@ -30764,7 +30764,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>1994.58</v>
+        <v>1991.79</v>
       </c>
     </row>
     <row r="498">
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>5382.62</v>
+        <v>5375.07</v>
       </c>
     </row>
     <row r="499">
@@ -30886,7 +30886,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>1402.93</v>
+        <v>1400.96</v>
       </c>
     </row>
     <row r="500">
@@ -30947,7 +30947,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>763.87</v>
+        <v>762.8</v>
       </c>
     </row>
     <row r="501">
@@ -31008,7 +31008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>1002.46</v>
+        <v>1003.75</v>
       </c>
     </row>
     <row r="502">
@@ -31069,7 +31069,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>876.75</v>
+        <v>877.88</v>
       </c>
     </row>
     <row r="503">
@@ -31130,7 +31130,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>3430.06</v>
+        <v>3434.46</v>
       </c>
     </row>
     <row r="504">
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>952.03</v>
+        <v>953.25</v>
       </c>
     </row>
     <row r="505">
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2354.39</v>
+        <v>2357.41</v>
       </c>
     </row>
     <row r="506">
@@ -31313,7 +31313,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>19506.39</v>
+        <v>19531.4</v>
       </c>
     </row>
     <row r="507">
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>926.46</v>
+        <v>927.65</v>
       </c>
     </row>
     <row r="508">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>859.22</v>
+        <v>860.3200000000001</v>
       </c>
     </row>
     <row r="509">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1025.06</v>
+        <v>1026.38</v>
       </c>
     </row>
     <row r="510">
@@ -31557,7 +31557,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>1717.07</v>
+        <v>1719.28</v>
       </c>
     </row>
     <row r="511">
@@ -31618,7 +31618,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>3269.8</v>
+        <v>3273.99</v>
       </c>
     </row>
     <row r="512">
@@ -31679,7 +31679,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>1719.65</v>
+        <v>1721.86</v>
       </c>
     </row>
     <row r="513">
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>25545</v>
+        <v>25577.75</v>
       </c>
     </row>
     <row r="514">
@@ -31801,7 +31801,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>869.9400000000001</v>
+        <v>871.05</v>
       </c>
     </row>
     <row r="515">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>1154.25</v>
+        <v>1155.73</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>4451.7</v>
+        <v>4457.41</v>
       </c>
     </row>
     <row r="517">
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>6071.91</v>
+        <v>6079.7</v>
       </c>
     </row>
     <row r="518">
@@ -32045,7 +32045,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>785.65</v>
+        <v>786.66</v>
       </c>
     </row>
     <row r="519">
@@ -32106,7 +32106,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>815.61</v>
+        <v>816.65</v>
       </c>
     </row>
     <row r="520">
@@ -32167,7 +32167,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>1565.51</v>
+        <v>1567.52</v>
       </c>
     </row>
     <row r="521">
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>927.9299999999999</v>
+        <v>929.12</v>
       </c>
     </row>
     <row r="522">
@@ -32289,7 +32289,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2886.47</v>
+        <v>2890.17</v>
       </c>
     </row>
     <row r="523">
@@ -32350,7 +32350,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>2006.15</v>
+        <v>2008.72</v>
       </c>
     </row>
     <row r="524">
@@ -32411,7 +32411,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>3123.39</v>
+        <v>3127.39</v>
       </c>
     </row>
     <row r="525">
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>1178.32</v>
+        <v>1179.83</v>
       </c>
     </row>
     <row r="526">
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>2267.14</v>
+        <v>2270.05</v>
       </c>
     </row>
     <row r="527">
@@ -32594,7 +32594,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>2710.08</v>
+        <v>2713.55</v>
       </c>
     </row>
     <row r="528">
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>2468.25</v>
+        <v>2471.41</v>
       </c>
     </row>
     <row r="529">
@@ -32716,7 +32716,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1155.71</v>
+        <v>1157.19</v>
       </c>
     </row>
     <row r="530">
@@ -32777,7 +32777,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>11836.19</v>
+        <v>11851.36</v>
       </c>
     </row>
     <row r="531">
@@ -32838,7 +32838,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>776.4</v>
+        <v>777.4</v>
       </c>
     </row>
     <row r="532">
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>1244.84</v>
+        <v>1246.43</v>
       </c>
     </row>
     <row r="533">
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>761.09</v>
+        <v>762.0599999999999</v>
       </c>
     </row>
     <row r="534">
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>1211.22</v>
+        <v>1212.77</v>
       </c>
     </row>
     <row r="535">
@@ -33082,7 +33082,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>1653.33</v>
+        <v>1655.44</v>
       </c>
     </row>
     <row r="536">
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>795.91</v>
+        <v>796.9299999999999</v>
       </c>
     </row>
     <row r="537">
@@ -33204,7 +33204,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>1635.96</v>
+        <v>1638.06</v>
       </c>
     </row>
     <row r="538">
@@ -33265,7 +33265,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>765.47</v>
+        <v>766.45</v>
       </c>
     </row>
     <row r="539">
@@ -33326,7 +33326,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1115.34</v>
+        <v>1116.77</v>
       </c>
     </row>
     <row r="540">
@@ -33387,7 +33387,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>9586.139999999999</v>
+        <v>9598.43</v>
       </c>
     </row>
     <row r="541">
@@ -33448,7 +33448,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>2353.73</v>
+        <v>2356.75</v>
       </c>
     </row>
     <row r="542">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>862.28</v>
+        <v>863.39</v>
       </c>
     </row>
     <row r="543">
@@ -33570,7 +33570,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>781.77</v>
+        <v>782.77</v>
       </c>
     </row>
     <row r="544">
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>3000.5</v>
+        <v>3004.35</v>
       </c>
     </row>
     <row r="545">
@@ -33692,7 +33692,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>7614.13</v>
+        <v>7623.89</v>
       </c>
     </row>
     <row r="546">
@@ -33753,7 +33753,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>763.1900000000001</v>
+        <v>764.17</v>
       </c>
     </row>
     <row r="547">
@@ -33814,7 +33814,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>2851.46</v>
+        <v>2855.12</v>
       </c>
     </row>
     <row r="548">
@@ -33875,7 +33875,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>2471.85</v>
+        <v>2475.02</v>
       </c>
     </row>
     <row r="549">
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>806.2</v>
+        <v>811.75</v>
       </c>
     </row>
     <row r="550">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>7826.07</v>
+        <v>7879.94</v>
       </c>
     </row>
     <row r="551">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>1038.43</v>
+        <v>1045.58</v>
       </c>
     </row>
     <row r="552">
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>6990.92</v>
+        <v>7039.04</v>
       </c>
     </row>
     <row r="553">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>1738.49</v>
+        <v>1750.45</v>
       </c>
     </row>
     <row r="554">
@@ -34241,7 +34241,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>7970.19</v>
+        <v>8025.05</v>
       </c>
     </row>
     <row r="555">
@@ -34302,7 +34302,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>4359.42</v>
+        <v>4389.42</v>
       </c>
     </row>
     <row r="556">
@@ -34363,7 +34363,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>1360.2</v>
+        <v>1369.57</v>
       </c>
     </row>
     <row r="557">
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>8767.74</v>
+        <v>8828.09</v>
       </c>
     </row>
     <row r="558">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>9713.65</v>
+        <v>9780.51</v>
       </c>
     </row>
     <row r="559">
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>4126.38</v>
+        <v>4154.79</v>
       </c>
     </row>
     <row r="560">
@@ -34607,7 +34607,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>1328.59</v>
+        <v>1337.74</v>
       </c>
     </row>
     <row r="561">
@@ -34668,7 +34668,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1014.22</v>
+        <v>1021.21</v>
       </c>
     </row>
     <row r="562">
@@ -34729,7 +34729,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>4279.46</v>
+        <v>4308.91</v>
       </c>
     </row>
     <row r="563">
@@ -34790,7 +34790,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>764.49</v>
+        <v>769.76</v>
       </c>
     </row>
     <row r="564">
@@ -34851,7 +34851,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>1179.18</v>
+        <v>1187.3</v>
       </c>
     </row>
     <row r="565">
@@ -34912,7 +34912,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>6245.87</v>
+        <v>6288.86</v>
       </c>
     </row>
     <row r="566">
@@ -34973,7 +34973,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>3174.51</v>
+        <v>3196.36</v>
       </c>
     </row>
     <row r="567">
@@ -35034,7 +35034,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>3252.93</v>
+        <v>3275.32</v>
       </c>
     </row>
     <row r="568">
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>2731.16</v>
+        <v>2749.95</v>
       </c>
     </row>
     <row r="569">
@@ -35156,7 +35156,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>6146.89</v>
+        <v>6189.2</v>
       </c>
     </row>
     <row r="570">
@@ -35217,7 +35217,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>1665.49</v>
+        <v>1676.95</v>
       </c>
     </row>
     <row r="571">
@@ -35278,7 +35278,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>809.54</v>
+        <v>815.11</v>
       </c>
     </row>
     <row r="572">
@@ -35339,7 +35339,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>1091.49</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="573">
@@ -35400,7 +35400,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>2550.69</v>
+        <v>2568.24</v>
       </c>
     </row>
     <row r="574">
@@ -35461,7 +35461,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>6175.51</v>
+        <v>6218.02</v>
       </c>
     </row>
     <row r="575">
@@ -35522,7 +35522,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1396.74</v>
+        <v>1406.36</v>
       </c>
     </row>
     <row r="576">
@@ -35583,7 +35583,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>2771.11</v>
+        <v>2790.18</v>
       </c>
     </row>
     <row r="577">
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>4446.12</v>
+        <v>4476.72</v>
       </c>
     </row>
     <row r="578">
@@ -35705,7 +35705,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>4524.79</v>
+        <v>4555.94</v>
       </c>
     </row>
     <row r="579">
@@ -35766,7 +35766,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>1155.73</v>
+        <v>1163.69</v>
       </c>
     </row>
     <row r="580">
@@ -35827,7 +35827,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>1220.75</v>
+        <v>1231.19</v>
       </c>
     </row>
     <row r="581">
@@ -35888,7 +35888,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>6741.41</v>
+        <v>6799.02</v>
       </c>
     </row>
     <row r="582">
@@ -35949,7 +35949,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>1421.81</v>
+        <v>1433.96</v>
       </c>
     </row>
     <row r="583">
@@ -36010,7 +36010,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>918.8</v>
+        <v>926.65</v>
       </c>
     </row>
     <row r="584">
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>2477.16</v>
+        <v>2498.33</v>
       </c>
     </row>
     <row r="585">
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>6004.36</v>
+        <v>6055.67</v>
       </c>
     </row>
     <row r="586">
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>1091.07</v>
+        <v>1100.39</v>
       </c>
     </row>
     <row r="587">
@@ -36254,7 +36254,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>1381</v>
+        <v>1392.8</v>
       </c>
     </row>
     <row r="588">
@@ -36315,7 +36315,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1303.22</v>
+        <v>1314.36</v>
       </c>
     </row>
     <row r="589">
@@ -36376,7 +36376,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>5283.52</v>
+        <v>5328.67</v>
       </c>
     </row>
     <row r="590">
@@ -36437,7 +36437,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>4104.71</v>
+        <v>4139.79</v>
       </c>
     </row>
     <row r="591">
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>7670.13</v>
+        <v>7735.68</v>
       </c>
     </row>
     <row r="592">
@@ -36559,7 +36559,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>969.5</v>
+        <v>977.78</v>
       </c>
     </row>
     <row r="593">
@@ -36620,7 +36620,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>764.34</v>
+        <v>770.87</v>
       </c>
     </row>
     <row r="594">
@@ -36681,7 +36681,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>3276.05</v>
+        <v>3304.04</v>
       </c>
     </row>
     <row r="595">
@@ -36742,7 +36742,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>1091.49</v>
+        <v>1100.82</v>
       </c>
     </row>
     <row r="596">
@@ -36803,7 +36803,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>1882.39</v>
+        <v>1898.47</v>
       </c>
     </row>
     <row r="597">
@@ -36864,7 +36864,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>4329.22</v>
+        <v>4366.22</v>
       </c>
     </row>
     <row r="598">
@@ -36925,7 +36925,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>4602.81</v>
+        <v>4642.14</v>
       </c>
     </row>
     <row r="599">
@@ -36986,7 +36986,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>18315.06</v>
+        <v>18471.58</v>
       </c>
     </row>
     <row r="600">
@@ -37047,7 +37047,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>43268.77</v>
+        <v>43638.53</v>
       </c>
     </row>
     <row r="601">
@@ -37108,7 +37108,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>18281.7</v>
+        <v>18437.94</v>
       </c>
     </row>
     <row r="602">
@@ -37169,7 +37169,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>1267.53</v>
+        <v>1278.36</v>
       </c>
     </row>
     <row r="603">
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>2385.85</v>
+        <v>2406.24</v>
       </c>
     </row>
     <row r="604">
@@ -37291,7 +37291,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>5010.21</v>
+        <v>5053.03</v>
       </c>
     </row>
     <row r="605">
@@ -37352,7 +37352,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>1060.26</v>
+        <v>1069.32</v>
       </c>
     </row>
     <row r="606">
@@ -37413,7 +37413,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>5417.85</v>
+        <v>5464.15</v>
       </c>
     </row>
     <row r="607">
@@ -37474,7 +37474,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>1147.14</v>
+        <v>1156.94</v>
       </c>
     </row>
     <row r="608">
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>2031.73</v>
+        <v>2049.1</v>
       </c>
     </row>
     <row r="609">
@@ -37596,7 +37596,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>1087.98</v>
+        <v>1097.27</v>
       </c>
     </row>
     <row r="610">
@@ -37657,7 +37657,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>2444.43</v>
+        <v>2465.32</v>
       </c>
     </row>
     <row r="611">
@@ -37718,7 +37718,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>3944.61</v>
+        <v>3978.32</v>
       </c>
     </row>
     <row r="612">
@@ -37779,7 +37779,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>915.7</v>
+        <v>923.52</v>
       </c>
     </row>
     <row r="613">
@@ -37840,7 +37840,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>768.4299999999999</v>
+        <v>774.99</v>
       </c>
     </row>
     <row r="614">
@@ -37901,7 +37901,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>4383.19</v>
+        <v>4420.65</v>
       </c>
     </row>
     <row r="615">
@@ -37962,7 +37962,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>5556.64</v>
+        <v>5604.13</v>
       </c>
     </row>
     <row r="616">
@@ -38023,7 +38023,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>6549.01</v>
+        <v>6604.97</v>
       </c>
     </row>
     <row r="617">
@@ -38084,7 +38084,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>5778.55</v>
+        <v>5840.54</v>
       </c>
     </row>
     <row r="618">
@@ -38145,7 +38145,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>768.17</v>
+        <v>776.41</v>
       </c>
     </row>
     <row r="619">
@@ -38206,7 +38206,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>3712.02</v>
+        <v>3751.84</v>
       </c>
     </row>
     <row r="620">
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>4622.6</v>
+        <v>4672.18</v>
       </c>
     </row>
     <row r="621">
@@ -38328,7 +38328,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>1786.76</v>
+        <v>1805.93</v>
       </c>
     </row>
     <row r="622">
@@ -38389,7 +38389,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>1554.44</v>
+        <v>1571.11</v>
       </c>
     </row>
     <row r="623">
@@ -38450,7 +38450,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>2775.8</v>
+        <v>2805.57</v>
       </c>
     </row>
     <row r="624">
@@ -38511,7 +38511,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>4701.35</v>
+        <v>4751.78</v>
       </c>
     </row>
     <row r="625">
@@ -38572,7 +38572,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>6471.58</v>
+        <v>6541</v>
       </c>
     </row>
     <row r="626">
@@ -38633,7 +38633,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>786.9</v>
+        <v>795.34</v>
       </c>
     </row>
     <row r="627">
@@ -38694,7 +38694,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>3017.33</v>
+        <v>3049.7</v>
       </c>
     </row>
     <row r="628">
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>1700.19</v>
+        <v>1718.43</v>
       </c>
     </row>
     <row r="629">
@@ -38816,7 +38816,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>34498.8</v>
+        <v>34868.86</v>
       </c>
     </row>
     <row r="630">
@@ -38877,7 +38877,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>54573.35</v>
+        <v>55158.73</v>
       </c>
     </row>
     <row r="631">
@@ -38938,7 +38938,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>2919.61</v>
+        <v>2950.92</v>
       </c>
     </row>
     <row r="632">
@@ -38999,7 +38999,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>3056.19</v>
+        <v>3088.97</v>
       </c>
     </row>
     <row r="633">
@@ -39060,7 +39060,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>13211.04</v>
+        <v>13352.75</v>
       </c>
     </row>
     <row r="634">
@@ -39121,7 +39121,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>8151.87</v>
+        <v>8239.309999999999</v>
       </c>
     </row>
     <row r="635">
@@ -39182,7 +39182,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>64929.25</v>
+        <v>65727.23</v>
       </c>
     </row>
     <row r="636">
@@ -39243,7 +39243,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>1489.83</v>
+        <v>1508.14</v>
       </c>
     </row>
     <row r="637">
@@ -39304,7 +39304,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>1444.33</v>
+        <v>1462.08</v>
       </c>
     </row>
     <row r="638">
@@ -39365,7 +39365,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>38202.43</v>
+        <v>38671.94</v>
       </c>
     </row>
     <row r="639">
@@ -39426,7 +39426,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>6168.36</v>
+        <v>6244.17</v>
       </c>
     </row>
     <row r="640">
@@ -39487,7 +39487,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>3142.08</v>
+        <v>3180.69</v>
       </c>
     </row>
     <row r="641">
@@ -39548,7 +39548,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>6390.19</v>
+        <v>6468.72</v>
       </c>
     </row>
     <row r="642">
@@ -39609,7 +39609,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>1003.19</v>
+        <v>1015.52</v>
       </c>
     </row>
     <row r="643">
@@ -39670,7 +39670,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>4038.31</v>
+        <v>4087.94</v>
       </c>
     </row>
     <row r="644">
@@ -39731,7 +39731,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>868.51</v>
+        <v>879.1900000000001</v>
       </c>
     </row>
     <row r="645">
@@ -39792,7 +39792,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>1082.92</v>
+        <v>1096.23</v>
       </c>
     </row>
     <row r="646">
@@ -39853,7 +39853,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>1224.56</v>
+        <v>1239.61</v>
       </c>
     </row>
     <row r="647">
@@ -39914,7 +39914,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>10851.55</v>
+        <v>10984.91</v>
       </c>
     </row>
     <row r="648">
@@ -39975,7 +39975,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>45397.9</v>
+        <v>45955.84</v>
       </c>
     </row>
     <row r="649">
@@ -40036,7 +40036,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>1508.54</v>
+        <v>1527.08</v>
       </c>
     </row>
     <row r="650">
@@ -40097,7 +40097,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>3375.09</v>
+        <v>3416.57</v>
       </c>
     </row>
     <row r="651">
@@ -40158,7 +40158,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>15594.42</v>
+        <v>15786.08</v>
       </c>
     </row>
     <row r="652">
@@ -40219,7 +40219,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>4651.05</v>
+        <v>4708.21</v>
       </c>
     </row>
     <row r="653">
@@ -40280,7 +40280,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>2680.92</v>
+        <v>2713.87</v>
       </c>
     </row>
     <row r="654">
@@ -40341,7 +40341,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>20475.37</v>
+        <v>20727.02</v>
       </c>
     </row>
     <row r="655">
@@ -40402,7 +40402,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>15119.66</v>
+        <v>15305.48</v>
       </c>
     </row>
     <row r="656">
@@ -40463,7 +40463,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>27243.76</v>
+        <v>27578.59</v>
       </c>
     </row>
     <row r="657">
@@ -40524,7 +40524,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>25061.64</v>
+        <v>25369.65</v>
       </c>
     </row>
     <row r="658">
@@ -40585,7 +40585,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>12736.74</v>
+        <v>12893.28</v>
       </c>
     </row>
     <row r="659">
@@ -40646,7 +40646,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>13097.8</v>
+        <v>13258.78</v>
       </c>
     </row>
     <row r="660">
@@ -40707,7 +40707,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>7179.16</v>
+        <v>7271.41</v>
       </c>
     </row>
     <row r="661">
@@ -40768,7 +40768,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>3232.48</v>
+        <v>3274.02</v>
       </c>
     </row>
     <row r="662">
@@ -40829,7 +40829,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>2641.11</v>
+        <v>2675.04</v>
       </c>
     </row>
     <row r="663">
@@ -40890,7 +40890,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>785.1799999999999</v>
+        <v>795.27</v>
       </c>
     </row>
     <row r="664">
@@ -40951,7 +40951,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>6375.69</v>
+        <v>6457.61</v>
       </c>
     </row>
     <row r="665">
@@ -41012,7 +41012,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>968.78</v>
+        <v>981.23</v>
       </c>
     </row>
     <row r="666">
@@ -41073,7 +41073,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>7046.38</v>
+        <v>7136.92</v>
       </c>
     </row>
     <row r="667">
@@ -41134,7 +41134,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>1388.68</v>
+        <v>1406.53</v>
       </c>
     </row>
     <row r="668">
@@ -41195,7 +41195,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>2104.8</v>
+        <v>2131.84</v>
       </c>
     </row>
     <row r="669">
@@ -41256,7 +41256,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>9725</v>
+        <v>9849.959999999999</v>
       </c>
     </row>
     <row r="670">
@@ -41317,7 +41317,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>2502.91</v>
+        <v>2535.07</v>
       </c>
     </row>
     <row r="671">
@@ -41378,7 +41378,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>5281.23</v>
+        <v>5349.09</v>
       </c>
     </row>
     <row r="672">
@@ -41439,7 +41439,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>41696.81</v>
+        <v>42232.6</v>
       </c>
     </row>
     <row r="673">
@@ -41500,7 +41500,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>36285.3</v>
+        <v>36751.55</v>
       </c>
     </row>
     <row r="674">
@@ -41561,7 +41561,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>6268.29</v>
+        <v>6348.83</v>
       </c>
     </row>
     <row r="675">
@@ -41622,7 +41622,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>1904</v>
+        <v>1928.46</v>
       </c>
     </row>
     <row r="676">
@@ -41683,7 +41683,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2459.43</v>
+        <v>2491.04</v>
       </c>
     </row>
     <row r="677">
@@ -41744,7 +41744,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>3953.32</v>
+        <v>4004.12</v>
       </c>
     </row>
     <row r="678">
@@ -41805,7 +41805,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>1200.05</v>
+        <v>1215.47</v>
       </c>
     </row>
     <row r="679">
@@ -41866,7 +41866,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>12289.79</v>
+        <v>12447.71</v>
       </c>
     </row>
     <row r="680">
@@ -41927,7 +41927,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>2029.51</v>
+        <v>2055.59</v>
       </c>
     </row>
     <row r="681">
@@ -41988,7 +41988,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>1248.94</v>
+        <v>1264.99</v>
       </c>
     </row>
     <row r="682">
@@ -42049,7 +42049,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>1087.09</v>
+        <v>1101.06</v>
       </c>
     </row>
     <row r="683">
@@ -42110,7 +42110,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>6495.03</v>
+        <v>6578.49</v>
       </c>
     </row>
     <row r="684">
@@ -42171,7 +42171,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>2095.04</v>
+        <v>2106.5</v>
       </c>
     </row>
     <row r="685">
@@ -42232,7 +42232,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>765.05</v>
+        <v>769.23</v>
       </c>
     </row>
     <row r="686">
@@ -42293,7 +42293,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>1154.88</v>
+        <v>1161.2</v>
       </c>
     </row>
     <row r="687">
@@ -42354,7 +42354,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>1664.4</v>
+        <v>1673.51</v>
       </c>
     </row>
     <row r="688">
@@ -42415,7 +42415,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>1929.6</v>
+        <v>1940.15</v>
       </c>
     </row>
     <row r="689">
@@ -42476,7 +42476,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>3515.99</v>
+        <v>3535.22</v>
       </c>
     </row>
     <row r="690">
@@ -42537,7 +42537,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>9060.969999999999</v>
+        <v>9110.52</v>
       </c>
     </row>
     <row r="691">
@@ -42598,7 +42598,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>1221.42</v>
+        <v>1228.1</v>
       </c>
     </row>
     <row r="692">
@@ -42659,7 +42659,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>11202</v>
+        <v>11263.26</v>
       </c>
     </row>
     <row r="693">
@@ -42720,7 +42720,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>811.98</v>
+        <v>816.42</v>
       </c>
     </row>
     <row r="694">
@@ -42781,7 +42781,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>1014.07</v>
+        <v>1019.62</v>
       </c>
     </row>
     <row r="695">
@@ -42842,7 +42842,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>893.45</v>
+        <v>898.33</v>
       </c>
     </row>
     <row r="696">
@@ -42903,7 +42903,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>14724.41</v>
+        <v>14804.93</v>
       </c>
     </row>
     <row r="697">
@@ -42964,7 +42964,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>1091.45</v>
+        <v>1097.42</v>
       </c>
     </row>
     <row r="698">
@@ -43025,7 +43025,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>3723.62</v>
+        <v>3743.99</v>
       </c>
     </row>
     <row r="699">
@@ -43086,7 +43086,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>3633.55</v>
+        <v>3653.42</v>
       </c>
     </row>
     <row r="700">
@@ -43147,7 +43147,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>2389.99</v>
+        <v>2403.06</v>
       </c>
     </row>
     <row r="701">
@@ -43208,7 +43208,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>3252.46</v>
+        <v>3270.24</v>
       </c>
     </row>
     <row r="702">
@@ -43269,7 +43269,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>2758.73</v>
+        <v>2773.82</v>
       </c>
     </row>
     <row r="703">
@@ -43330,7 +43330,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>1838.76</v>
+        <v>1848.81</v>
       </c>
     </row>
     <row r="704">
@@ -43391,7 +43391,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>2399.25</v>
+        <v>2412.38</v>
       </c>
     </row>
     <row r="705">
@@ -43452,7 +43452,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>5698.36</v>
+        <v>5729.52</v>
       </c>
     </row>
     <row r="706">
@@ -43513,7 +43513,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>1208.46</v>
+        <v>1215.07</v>
       </c>
     </row>
     <row r="707">
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>842.97</v>
+        <v>847.58</v>
       </c>
     </row>
     <row r="708">
@@ -43635,7 +43635,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>5412.69</v>
+        <v>5442.29</v>
       </c>
     </row>
     <row r="709">
@@ -43696,7 +43696,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>3927.86</v>
+        <v>3949.34</v>
       </c>
     </row>
     <row r="710">
@@ -43757,7 +43757,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>2178.64</v>
+        <v>2190.56</v>
       </c>
     </row>
     <row r="711">
@@ -43818,7 +43818,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>2970.16</v>
+        <v>2986.4</v>
       </c>
     </row>
     <row r="712">
@@ -43879,7 +43879,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>788.16</v>
+        <v>792.47</v>
       </c>
     </row>
     <row r="713">
@@ -43940,7 +43940,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1042.38</v>
+        <v>1048.08</v>
       </c>
     </row>
     <row r="714">
@@ -44001,7 +44001,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>6548.59</v>
+        <v>6584.4</v>
       </c>
     </row>
     <row r="715">
@@ -44062,7 +44062,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>7917.25</v>
+        <v>7960.55</v>
       </c>
     </row>
     <row r="716">
@@ -44123,7 +44123,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>13518.25</v>
+        <v>13592.18</v>
       </c>
     </row>
     <row r="717">
@@ -44184,7 +44184,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>2156.69</v>
+        <v>2168.48</v>
       </c>
     </row>
     <row r="718">
@@ -44245,7 +44245,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>927.89</v>
+        <v>932.96</v>
       </c>
     </row>
     <row r="719">
@@ -44306,7 +44306,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>1679.74</v>
+        <v>1688.93</v>
       </c>
     </row>
     <row r="720">
@@ -44367,7 +44367,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>1637.86</v>
+        <v>1646.81</v>
       </c>
     </row>
     <row r="721">
@@ -44428,7 +44428,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>1393.03</v>
+        <v>1400.65</v>
       </c>
     </row>
     <row r="722">
@@ -44489,7 +44489,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>6598.79</v>
+        <v>6634.88</v>
       </c>
     </row>
     <row r="723">
@@ -44550,7 +44550,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>4912.55</v>
+        <v>4939.42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/dic-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36600,7 +36600,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -37393,7 +37393,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -38857,7 +38857,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -39345,7 +39345,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39711,7 +39711,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -40260,7 +40260,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40382,7 +40382,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40931,7 +40931,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -41541,7 +41541,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41602,7 +41602,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41663,7 +41663,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41785,7 +41785,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -42090,7 +42090,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -43188,7 +43188,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43432,7 +43432,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43737,7 +43737,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -43798,7 +43798,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -43859,7 +43859,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -44286,7 +44286,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/dic-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/dic-2025.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Osorno</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Instituto Nacional de Neurocirugía</t>
+          <t>Instituto de Neurocirugía</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Superintendencia de Salud</t>
+          <t>SUPERINTENDENCIA DE SALUD</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Museo Marítimo Nacional</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Departamento de Salud Parral</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Departamento De Educacion Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE FINANZAS DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL  E INMOB MAS COMERCIO LTDA.</t>
+          <t>Sociedad Comercial  e Inmob Mas Comercio Ltda.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Superintendencia de Salud</t>
+          <t>SUPERINTENDENCIA DE SALUD</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificacion</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FRE</t>
+          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FREI MONTALVA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Libertador Gral. Bernardo O´higgins</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO CONTROL FINANCIERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE MARINA HOSP NAVAL ALMIR</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de Magallanes y la Antartica</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Agencia de Promocion de la inversion extranjera</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Departamento De Educacion Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Santiago Oriente</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16221,12 +16221,12 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SERPLAC LOS RIOS</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18478,7 +18478,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>IIIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18539,12 +18539,12 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19637,7 +19637,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21955,7 +21955,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Escuadrilla de Abastecimiento del Edificio FF.AA.</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
@@ -22565,7 +22565,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Servicio Agricola y Ganadero</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -23419,7 +23419,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -23592,7 +23592,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>IIIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24334,7 +24334,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -24944,7 +24944,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -25371,7 +25371,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -25432,7 +25432,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25615,7 +25615,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -25859,7 +25859,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -25981,7 +25981,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -26418,7 +26418,7 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
@@ -26469,7 +26469,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27262,7 +27262,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALPARAÍSO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE VALPARAISO</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -27811,7 +27811,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -27994,7 +27994,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -28055,7 +28055,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -28543,7 +28543,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -28726,7 +28726,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -28970,7 +28970,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>ESCUELA DE GRUMETES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -29153,7 +29153,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -29519,7 +29519,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -30068,7 +30068,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30251,7 +30251,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -32203,7 +32203,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32498,7 +32498,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -32569,7 +32569,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -33118,7 +33118,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -33372,7 +33372,7 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
@@ -33606,7 +33606,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Secretaría Ministerial de Educación - RM</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -33789,7 +33789,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -33911,7 +33911,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -34582,7 +34582,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -35009,7 +35009,7 @@
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -35314,7 +35314,7 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -35375,7 +35375,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Hospital San Jose - Casablanca</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -35863,7 +35863,7 @@
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -36168,7 +36168,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -36229,7 +36229,7 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>SERPLAC III Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -36473,7 +36473,7 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -36717,7 +36717,7 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales VII Región</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -36900,7 +36900,7 @@
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37449,7 +37449,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Hospital San Jose - Casablanca</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -37998,7 +37998,7 @@
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -38364,7 +38364,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -38913,7 +38913,7 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -38974,7 +38974,7 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALPARAÍSO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE VALPARAISO</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -39462,7 +39462,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -39645,7 +39645,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>Dirección Provincial de Educación Quillota - Petorca</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -40072,7 +40072,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -40255,7 +40255,7 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION VI REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -40804,12 +40804,12 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40926,7 +40926,7 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>ESCUELA DE GRUMETES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -40987,7 +40987,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Iquique</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -41353,7 +41353,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -42034,7 +42034,7 @@
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
@@ -42207,7 +42207,7 @@
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE EDUCACION,SALUD,CULTURA Y</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION,SALUD,CULTURA Y ATENCION AL MENOR,</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -42268,7 +42268,7 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -42390,7 +42390,7 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -42451,7 +42451,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -43122,7 +43122,7 @@
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -43488,7 +43488,7 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>SERPLAC III Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -43671,7 +43671,7 @@
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -44037,7 +44037,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -44286,7 +44286,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44525,7 +44525,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/dic-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/dic-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1590,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1781,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1846,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1911,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1976,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2163,11 @@
           <t>78.069.505-6</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2228,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2293,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2358,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2545,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2610,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2675,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2740,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2805,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2870,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2935,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3061,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3126,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3374,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3439,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3504,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3569,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3634,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3699,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3764,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3829,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3894,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3959,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4085,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4150,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4215,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4280,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4345,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4410,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4475,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4540,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4666,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4731,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4796,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4922,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4987,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5052,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5117,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5182,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5308,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5373,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5438,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5503,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5568,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5633,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5698,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5885,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5950,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6015,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6141,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6450,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6515,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6767,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6832,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6958,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7084,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7210,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7275,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7340,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7466,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7531,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7596,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7661,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7726,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7791,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7856,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7921,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7986,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8051,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8238,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8303,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8368,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8433,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8620,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8685,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8750,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8876,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8941,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9006,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9071,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9136,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9201,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9266,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9331,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9457,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9522,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9587,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9652,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9717,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9782,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10030,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10095,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10160,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10225,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10351,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10477,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10542,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10790,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10855,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10920,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11046,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11172,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11237,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11302,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11367,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11432,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11497,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11562,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11810,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11936,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12001,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12066,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12192,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12257,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12383,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12448,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12513,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12578,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12643,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12708,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12773,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12960,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13025,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13090,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13155,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13220,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13285,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13411,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13598,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13663,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13728,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13793,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13858,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13923,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13988,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14053,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14179,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14244,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14309,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14374,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14439,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14504,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14569,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14634,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14699,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14764,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14829,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14955,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15268,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15333,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15459,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15524,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15589,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15654,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15719,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15784,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15910,11 @@
           <t>77.743.075-0</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15975,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16040,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16227,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16292,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16357,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16422,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16487,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16552,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16678,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16743,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16930,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16995,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17060,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17125,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17190,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17316,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17381,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17446,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17511,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17637,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17702,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17767,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17832,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17958,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18023,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18088,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18336,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18523,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18588,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18653,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18718,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18783,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18848,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18913,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19039,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19104,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19169,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19234,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19299,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19364,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19429,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19494,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19620,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19746,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19811,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19937,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20002,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20128,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20193,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20258,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20323,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20449,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20636,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20762,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20888,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20953,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21018,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21083,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21148,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21213,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21278,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21343,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21408,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21473,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21660,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21725,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21790,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21855,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21920,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21985,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22050,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22115,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22180,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22245,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22310,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22436,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22501,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22566,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22631,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22696,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22822,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22887,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22952,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23082,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23147,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23334,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23399,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23525,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23590,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23842,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23907,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23972,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24037,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24102,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24228,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24293,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24358,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24423,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24488,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24553,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24679,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24805,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +24870,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24935,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25061,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25187,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25252,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25439,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25504,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25630,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25695,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25760,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25825,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25890,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25955,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26020,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26085,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26150,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26215,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26280,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26345,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26532,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26597,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26662,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26727,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26792,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26857,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26922,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +26987,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27178,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27243,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27308,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27373,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27438,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27503,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27568,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27816,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27881,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27946,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28011,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28076,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28141,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28206,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28332,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28458,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28523,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28649,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28714,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28779,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28844,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +28909,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29035,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29100,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29165,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29291,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29356,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29421,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29486,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29551,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29738,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29803,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29868,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +29994,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30059,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30124,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30189,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30254,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30563,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30628,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30693,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30758,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30823,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30888,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31014,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31079,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31144,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31270,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31396,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31522,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31652,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +31717,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31782,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31847,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31912,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +31977,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32042,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32168,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32233,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32359,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32424,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32489,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +32554,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32619,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32684,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32749,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32814,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +33062,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33127,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33314,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33440,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33505,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +33570,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33635,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33700,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33765,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33830,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33895,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34021,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34086,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34212,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34277,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34342,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34407,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +34594,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +34659,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34724,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34789,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +35037,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +35102,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35167,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +35232,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35297,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35427,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +35492,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +35557,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +35622,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35687,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35813,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +35878,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35943,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +36069,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34478,7 +36134,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +36199,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +36325,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36455,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +36520,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36585,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34966,7 +36650,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36776,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +36841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36906,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36971,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +37097,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +37162,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +37227,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +37292,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +37357,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37422,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +37548,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37613,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37800,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +37987,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +38052,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +38117,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +38182,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +38247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +38373,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +38438,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +38625,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38690,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38755,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37040,7 +38820,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +38885,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +39011,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +39076,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +39141,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37406,7 +39206,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +39271,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +39336,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +39401,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39466,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +39531,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +39596,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39722,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37955,7 +39787,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38016,7 +39852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38077,7 +39917,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +39982,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +40169,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +40234,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38443,7 +40299,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38626,7 +40486,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38748,7 +40612,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38809,7 +40677,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38992,7 +40864,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39053,7 +40929,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39114,7 +40994,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39236,7 +41120,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39419,7 +41307,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39480,7 +41372,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39541,7 +41437,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +41502,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +41567,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39785,7 +41693,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39907,7 +41819,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39968,7 +41884,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40029,7 +41949,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +42014,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40151,7 +42079,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40212,7 +42144,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40273,7 +42209,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40334,7 +42274,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40456,7 +42400,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +42465,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40578,7 +42530,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40639,7 +42595,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40700,7 +42660,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40761,7 +42725,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40822,7 +42790,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40883,7 +42855,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41066,7 +43042,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41188,7 +43168,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41249,7 +43233,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41310,7 +43298,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41432,7 +43424,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41493,7 +43489,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41554,7 +43554,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41615,7 +43619,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41737,7 +43745,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41859,7 +43871,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41920,7 +43936,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41981,7 +44001,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42225,7 +44249,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42286,7 +44314,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42347,7 +44379,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42408,7 +44444,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42469,7 +44509,11 @@
           <t>78.069.505-6</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42530,7 +44574,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42591,7 +44639,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42774,7 +44826,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42896,7 +44952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42957,7 +45017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43018,7 +45082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43079,7 +45147,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43201,7 +45273,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43262,7 +45338,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43323,7 +45403,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43506,7 +45590,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43567,7 +45655,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43689,7 +45781,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43872,7 +45968,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43933,7 +46033,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43994,7 +46098,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44055,7 +46163,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44116,7 +46228,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44177,7 +46293,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44299,7 +46419,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44421,7 +46545,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44482,7 +46610,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
